--- a/Assignments/Jan-May-2026/investment_and_portfolio_management_coursera/course2_portfolio_selection_and_risk_management/assignment3/frontier_uk_japan_part2.xlsx
+++ b/Assignments/Jan-May-2026/investment_and_portfolio_management_coursera/course2_portfolio_selection_and_risk_management/assignment3/frontier_uk_japan_part2.xlsx
@@ -450,10 +450,10 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>0.1497</v>
+        <v>0.1589</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2298</v>
+        <v>0.243</v>
       </c>
     </row>
     <row r="3">
@@ -461,10 +461,10 @@
         <v>0.01</v>
       </c>
       <c r="B3" t="n">
-        <v>0.149792</v>
+        <v>0.158808</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2287266813557177</v>
+        <v>0.2417271924380871</v>
       </c>
     </row>
     <row r="4">
@@ -472,10 +472,10 @@
         <v>0.02</v>
       </c>
       <c r="B4" t="n">
-        <v>0.149884</v>
+        <v>0.158716</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2276729071628858</v>
+        <v>0.2404709426438047</v>
       </c>
     </row>
     <row r="5">
@@ -483,10 +483,10 @@
         <v>0.03</v>
       </c>
       <c r="B5" t="n">
-        <v>0.149976</v>
+        <v>0.158624</v>
       </c>
       <c r="C5" t="n">
-        <v>0.2266389500416907</v>
+        <v>0.2392315114611785</v>
       </c>
     </row>
     <row r="6">
@@ -494,10 +494,10 @@
         <v>0.04</v>
       </c>
       <c r="B6" t="n">
-        <v>0.150068</v>
+        <v>0.158532</v>
       </c>
       <c r="C6" t="n">
-        <v>0.225625082435442</v>
+        <v>0.2380091616387907</v>
       </c>
     </row>
     <row r="7">
@@ -505,10 +505,10 @@
         <v>0.05</v>
       </c>
       <c r="B7" t="n">
-        <v>0.15016</v>
+        <v>0.15844</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2246315763644996</v>
+        <v>0.2368041576915405</v>
       </c>
     </row>
     <row r="8">
@@ -516,10 +516,10 @@
         <v>0.06</v>
       </c>
       <c r="B8" t="n">
-        <v>0.150252</v>
+        <v>0.158348</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2236587031707016</v>
+        <v>0.2356167657532036</v>
       </c>
     </row>
     <row r="9">
@@ -527,10 +527,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="B9" t="n">
-        <v>0.150344</v>
+        <v>0.158256</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2227067332524996</v>
+        <v>0.2344472534196125</v>
       </c>
     </row>
     <row r="10">
@@ -538,10 +538,10 @@
         <v>0.08</v>
       </c>
       <c r="B10" t="n">
-        <v>0.150436</v>
+        <v>0.158164</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2217759357910592</v>
+        <v>0.233295889582307</v>
       </c>
     </row>
     <row r="11">
@@ -549,10 +549,10 @@
         <v>0.09</v>
       </c>
       <c r="B11" t="n">
-        <v>0.150528</v>
+        <v>0.158072</v>
       </c>
       <c r="C11" t="n">
-        <v>0.220866578467635</v>
+        <v>0.2321629442525228</v>
       </c>
     </row>
     <row r="12">
@@ -560,10 +560,10 @@
         <v>0.1</v>
       </c>
       <c r="B12" t="n">
-        <v>0.15062</v>
+        <v>0.15798</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2199789271725817</v>
+        <v>0.2310486883754158</v>
       </c>
     </row>
     <row r="13">
@@ -571,10 +571,10 @@
         <v>0.11</v>
       </c>
       <c r="B13" t="n">
-        <v>0.150712</v>
+        <v>0.157888</v>
       </c>
       <c r="C13" t="n">
-        <v>0.2191132457064155</v>
+        <v>0.2299533936344493</v>
       </c>
     </row>
     <row r="14">
@@ -582,10 +582,10 @@
         <v>0.12</v>
       </c>
       <c r="B14" t="n">
-        <v>0.150804</v>
+        <v>0.157796</v>
       </c>
       <c r="C14" t="n">
-        <v>0.2182697954734003</v>
+        <v>0.2288773322458998</v>
       </c>
     </row>
     <row r="15">
@@ -593,10 +593,10 @@
         <v>0.13</v>
       </c>
       <c r="B15" t="n">
-        <v>0.150896</v>
+        <v>0.157704</v>
       </c>
       <c r="C15" t="n">
-        <v>0.2174488351681839</v>
+        <v>0.2278207767434744</v>
       </c>
     </row>
     <row r="16">
@@ -604,10 +604,10 @@
         <v>0.14</v>
       </c>
       <c r="B16" t="n">
-        <v>0.150988</v>
+        <v>0.157612</v>
       </c>
       <c r="C16" t="n">
-        <v>0.2166506204560698</v>
+        <v>0.226783999753069</v>
       </c>
     </row>
     <row r="17">
@@ -615,10 +615,10 @@
         <v>0.15</v>
       </c>
       <c r="B17" t="n">
-        <v>0.15108</v>
+        <v>0.15752</v>
       </c>
       <c r="C17" t="n">
-        <v>0.215875403647567</v>
+        <v>0.2257672737577348</v>
       </c>
     </row>
     <row r="18">
@@ -626,10 +626,10 @@
         <v>0.16</v>
       </c>
       <c r="B18" t="n">
-        <v>0.151172</v>
+        <v>0.157428</v>
       </c>
       <c r="C18" t="n">
-        <v>0.2151234333679155</v>
+        <v>0.2247708708529644</v>
       </c>
     </row>
     <row r="19">
@@ -637,10 +637,10 @@
         <v>0.17</v>
       </c>
       <c r="B19" t="n">
-        <v>0.151264</v>
+        <v>0.157336</v>
       </c>
       <c r="C19" t="n">
-        <v>0.2143949542223417</v>
+        <v>0.2237950624924509</v>
       </c>
     </row>
     <row r="20">
@@ -648,10 +648,10 @@
         <v>0.18</v>
       </c>
       <c r="B20" t="n">
-        <v>0.151356</v>
+        <v>0.157244</v>
       </c>
       <c r="C20" t="n">
-        <v>0.2136902064578534</v>
+        <v>0.2228401192245238</v>
       </c>
     </row>
     <row r="21">
@@ -659,10 +659,10 @@
         <v>0.19</v>
       </c>
       <c r="B21" t="n">
-        <v>0.151448</v>
+        <v>0.157152</v>
       </c>
       <c r="C21" t="n">
-        <v>0.2130094256224358</v>
+        <v>0.2219063104195102</v>
       </c>
     </row>
     <row r="22">
@@ -670,10 +670,10 @@
         <v>0.2</v>
       </c>
       <c r="B22" t="n">
-        <v>0.15154</v>
+        <v>0.15706</v>
       </c>
       <c r="C22" t="n">
-        <v>0.2123528422225613</v>
+        <v>0.2209939039883227</v>
       </c>
     </row>
     <row r="23">
@@ -681,10 +681,10 @@
         <v>0.21</v>
       </c>
       <c r="B23" t="n">
-        <v>0.151632</v>
+        <v>0.156968</v>
       </c>
       <c r="C23" t="n">
-        <v>0.2117206813799729</v>
+        <v>0.2201031660926303</v>
       </c>
     </row>
     <row r="24">
@@ -692,10 +692,10 @@
         <v>0.22</v>
       </c>
       <c r="B24" t="n">
-        <v>0.151724</v>
+        <v>0.156876</v>
       </c>
       <c r="C24" t="n">
-        <v>0.2111131624887468</v>
+        <v>0.2192343608470169</v>
       </c>
     </row>
     <row r="25">
@@ -703,10 +703,10 @@
         <v>0.23</v>
       </c>
       <c r="B25" t="n">
-        <v>0.151816</v>
+        <v>0.156784</v>
       </c>
       <c r="C25" t="n">
-        <v>0.2105304988736787</v>
+        <v>0.2183877500135939</v>
       </c>
     </row>
     <row r="26">
@@ -714,10 +714,10 @@
         <v>0.24</v>
       </c>
       <c r="B26" t="n">
-        <v>0.151908</v>
+        <v>0.156692</v>
       </c>
       <c r="C26" t="n">
-        <v>0.2099728974510758</v>
+        <v>0.2175635926895858</v>
       </c>
     </row>
     <row r="27">
@@ -725,10 +725,10 @@
         <v>0.25</v>
       </c>
       <c r="B27" t="n">
-        <v>0.152</v>
+        <v>0.1566</v>
       </c>
       <c r="C27" t="n">
-        <v>0.2094405583930677</v>
+        <v>0.2167621449884642</v>
       </c>
     </row>
     <row r="28">
@@ -736,10 +736,10 @@
         <v>0.26</v>
       </c>
       <c r="B28" t="n">
-        <v>0.152092</v>
+        <v>0.156508</v>
       </c>
       <c r="C28" t="n">
-        <v>0.2089336747965727</v>
+        <v>0.2159836597152664</v>
       </c>
     </row>
     <row r="29">
@@ -747,10 +747,10 @@
         <v>0.27</v>
       </c>
       <c r="B29" t="n">
-        <v>0.152184</v>
+        <v>0.156416</v>
       </c>
       <c r="C29" t="n">
-        <v>0.2084524323580802</v>
+        <v>0.2152283860367865</v>
       </c>
     </row>
     <row r="30">
@@ -758,10 +758,10 @@
         <v>0.28</v>
       </c>
       <c r="B30" t="n">
-        <v>0.152276</v>
+        <v>0.156324</v>
       </c>
       <c r="C30" t="n">
-        <v>0.2079970090554189</v>
+        <v>0.2144965691473875</v>
       </c>
     </row>
     <row r="31">
@@ -769,10 +769,10 @@
         <v>0.29</v>
       </c>
       <c r="B31" t="n">
-        <v>0.152368</v>
+        <v>0.156232</v>
       </c>
       <c r="C31" t="n">
-        <v>0.2075675748376899</v>
+        <v>0.2137884499312346</v>
       </c>
     </row>
     <row r="32">
@@ -780,10 +780,10 @@
         <v>0.3</v>
       </c>
       <c r="B32" t="n">
-        <v>0.15246</v>
+        <v>0.15614</v>
       </c>
       <c r="C32" t="n">
-        <v>0.2071642913245427</v>
+        <v>0.2131042646218043</v>
       </c>
     </row>
     <row r="33">
@@ -791,10 +791,10 @@
         <v>0.31</v>
       </c>
       <c r="B33" t="n">
-        <v>0.152552</v>
+        <v>0.156048</v>
       </c>
       <c r="C33" t="n">
-        <v>0.2067873115159632</v>
+        <v>0.2124442444595758</v>
       </c>
     </row>
     <row r="34">
@@ -802,10 +802,10 @@
         <v>0.32</v>
       </c>
       <c r="B34" t="n">
-        <v>0.152644</v>
+        <v>0.155956</v>
       </c>
       <c r="C34" t="n">
-        <v>0.2064367795137291</v>
+        <v>0.2118086153488568</v>
       </c>
     </row>
     <row r="35">
@@ -813,10 +813,10 @@
         <v>0.33</v>
       </c>
       <c r="B35" t="n">
-        <v>0.152736</v>
+        <v>0.155864</v>
       </c>
       <c r="C35" t="n">
-        <v>0.2061128302556636</v>
+        <v>0.2111975975147445</v>
       </c>
     </row>
     <row r="36">
@@ -824,10 +824,10 @@
         <v>0.34</v>
       </c>
       <c r="B36" t="n">
-        <v>0.152828</v>
+        <v>0.155772</v>
       </c>
       <c r="C36" t="n">
-        <v>0.2058155892637873</v>
+        <v>0.210611405161259</v>
       </c>
     </row>
     <row r="37">
@@ -835,10 +835,10 @@
         <v>0.35</v>
       </c>
       <c r="B37" t="n">
-        <v>0.15292</v>
+        <v>0.15568</v>
       </c>
       <c r="C37" t="n">
-        <v>0.2055451724074297</v>
+        <v>0.2100502461317292</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         <v>0.36</v>
       </c>
       <c r="B38" t="n">
-        <v>0.153012</v>
+        <v>0.155588</v>
       </c>
       <c r="C38" t="n">
-        <v>0.2053016856823149</v>
+        <v>0.2095143215725359</v>
       </c>
     </row>
     <row r="39">
@@ -857,10 +857,10 @@
         <v>0.37</v>
       </c>
       <c r="B39" t="n">
-        <v>0.153104</v>
+        <v>0.155496</v>
       </c>
       <c r="C39" t="n">
-        <v>0.2050852250065811</v>
+        <v>0.2090038256013511</v>
       </c>
     </row>
     <row r="40">
@@ -868,10 +868,10 @@
         <v>0.38</v>
       </c>
       <c r="B40" t="n">
-        <v>0.153196</v>
+        <v>0.155404</v>
       </c>
       <c r="C40" t="n">
-        <v>0.2048958760346337</v>
+        <v>0.2085189449810256</v>
       </c>
     </row>
     <row r="41">
@@ -879,10 +879,10 @@
         <v>0.39</v>
       </c>
       <c r="B41" t="n">
-        <v>0.153288</v>
+        <v>0.155312</v>
       </c>
       <c r="C41" t="n">
-        <v>0.2047337139896602</v>
+        <v>0.2080598588002981</v>
       </c>
     </row>
     <row r="42">
@@ -890,10 +890,10 @@
         <v>0.4</v>
       </c>
       <c r="B42" t="n">
-        <v>0.15338</v>
+        <v>0.15522</v>
       </c>
       <c r="C42" t="n">
-        <v>0.2045988035155631</v>
+        <v>0.2076267381625016</v>
       </c>
     </row>
     <row r="43">
@@ -901,10 +901,10 @@
         <v>0.41</v>
       </c>
       <c r="B43" t="n">
-        <v>0.153472</v>
+        <v>0.155128</v>
       </c>
       <c r="C43" t="n">
-        <v>0.204491198548984</v>
+        <v>0.2072197458834462</v>
       </c>
     </row>
     <row r="44">
@@ -912,10 +912,10 @@
         <v>0.42</v>
       </c>
       <c r="B44" t="n">
-        <v>0.153564</v>
+        <v>0.155036</v>
       </c>
       <c r="C44" t="n">
-        <v>0.2044109422120059</v>
+        <v>0.2068390361996497</v>
       </c>
     </row>
     <row r="45">
@@ -923,10 +923,10 @@
         <v>0.43</v>
       </c>
       <c r="B45" t="n">
-        <v>0.153656</v>
+        <v>0.154944</v>
       </c>
       <c r="C45" t="n">
-        <v>0.2043580667260287</v>
+        <v>0.2064847544880735</v>
       </c>
     </row>
     <row r="46">
@@ -934,10 +934,10 @@
         <v>0.44</v>
       </c>
       <c r="B46" t="n">
-        <v>0.153748</v>
+        <v>0.154852</v>
       </c>
       <c r="C46" t="n">
-        <v>0.2043325933472191</v>
+        <v>0.2061570369984978</v>
       </c>
     </row>
     <row r="47">
@@ -945,10 +945,10 @@
         <v>0.45</v>
       </c>
       <c r="B47" t="n">
-        <v>0.15384</v>
+        <v>0.15476</v>
       </c>
       <c r="C47" t="n">
-        <v>0.2043345323238341</v>
+        <v>0.2058560105996422</v>
       </c>
     </row>
     <row r="48">
@@ -956,10 +956,10 @@
         <v>0.46</v>
       </c>
       <c r="B48" t="n">
-        <v>0.153932</v>
+        <v>0.154668</v>
       </c>
       <c r="C48" t="n">
-        <v>0.2043638828756197</v>
+        <v>0.2055817925400983</v>
       </c>
     </row>
     <row r="49">
@@ -967,10 +967,10 @@
         <v>0.47</v>
       </c>
       <c r="B49" t="n">
-        <v>0.154024</v>
+        <v>0.154576</v>
       </c>
       <c r="C49" t="n">
-        <v>0.2044206331953798</v>
+        <v>0.2053344902250959</v>
       </c>
     </row>
     <row r="50">
@@ -978,10 +978,10 @@
         <v>0.48</v>
       </c>
       <c r="B50" t="n">
-        <v>0.154116</v>
+        <v>0.154484</v>
       </c>
       <c r="C50" t="n">
-        <v>0.2045047604727088</v>
+        <v>0.2051142010100715</v>
       </c>
     </row>
     <row r="51">
@@ -989,10 +989,10 @@
         <v>0.49</v>
       </c>
       <c r="B51" t="n">
-        <v>0.154208</v>
+        <v>0.154392</v>
       </c>
       <c r="C51" t="n">
-        <v>0.2046162309397766</v>
+        <v>0.2049210120119457</v>
       </c>
     </row>
     <row r="52">
@@ -1011,10 +1011,10 @@
         <v>0.51</v>
       </c>
       <c r="B53" t="n">
-        <v>0.154392</v>
+        <v>0.154208</v>
       </c>
       <c r="C53" t="n">
-        <v>0.2049210120119457</v>
+        <v>0.2046162309397766</v>
       </c>
     </row>
     <row r="54">
@@ -1022,10 +1022,10 @@
         <v>0.52</v>
       </c>
       <c r="B54" t="n">
-        <v>0.154484</v>
+        <v>0.154116</v>
       </c>
       <c r="C54" t="n">
-        <v>0.2051142010100715</v>
+        <v>0.2045047604727088</v>
       </c>
     </row>
     <row r="55">
@@ -1033,10 +1033,10 @@
         <v>0.53</v>
       </c>
       <c r="B55" t="n">
-        <v>0.154576</v>
+        <v>0.154024</v>
       </c>
       <c r="C55" t="n">
-        <v>0.2053344902250959</v>
+        <v>0.2044206331953798</v>
       </c>
     </row>
     <row r="56">
@@ -1044,10 +1044,10 @@
         <v>0.54</v>
       </c>
       <c r="B56" t="n">
-        <v>0.154668</v>
+        <v>0.153932</v>
       </c>
       <c r="C56" t="n">
-        <v>0.2055817925400983</v>
+        <v>0.2043638828756197</v>
       </c>
     </row>
     <row r="57">
@@ -1055,10 +1055,10 @@
         <v>0.55</v>
       </c>
       <c r="B57" t="n">
-        <v>0.15476</v>
+        <v>0.15384</v>
       </c>
       <c r="C57" t="n">
-        <v>0.2058560105996422</v>
+        <v>0.2043345323238341</v>
       </c>
     </row>
     <row r="58">
@@ -1066,10 +1066,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="B58" t="n">
-        <v>0.154852</v>
+        <v>0.153748</v>
       </c>
       <c r="C58" t="n">
-        <v>0.2061570369984978</v>
+        <v>0.2043325933472191</v>
       </c>
     </row>
     <row r="59">
@@ -1077,10 +1077,10 @@
         <v>0.57</v>
       </c>
       <c r="B59" t="n">
-        <v>0.154944</v>
+        <v>0.153656</v>
       </c>
       <c r="C59" t="n">
-        <v>0.2064847544880735</v>
+        <v>0.2043580667260287</v>
       </c>
     </row>
     <row r="60">
@@ -1088,10 +1088,10 @@
         <v>0.58</v>
       </c>
       <c r="B60" t="n">
-        <v>0.155036</v>
+        <v>0.153564</v>
       </c>
       <c r="C60" t="n">
-        <v>0.2068390361996497</v>
+        <v>0.2044109422120058</v>
       </c>
     </row>
     <row r="61">
@@ -1099,10 +1099,10 @@
         <v>0.59</v>
       </c>
       <c r="B61" t="n">
-        <v>0.155128</v>
+        <v>0.153472</v>
       </c>
       <c r="C61" t="n">
-        <v>0.2072197458834461</v>
+        <v>0.204491198548984</v>
       </c>
     </row>
     <row r="62">
@@ -1110,10 +1110,10 @@
         <v>0.6</v>
       </c>
       <c r="B62" t="n">
-        <v>0.15522</v>
+        <v>0.15338</v>
       </c>
       <c r="C62" t="n">
-        <v>0.2076267381625016</v>
+        <v>0.2045988035155631</v>
       </c>
     </row>
     <row r="63">
@@ -1121,10 +1121,10 @@
         <v>0.61</v>
       </c>
       <c r="B63" t="n">
-        <v>0.155312</v>
+        <v>0.153288</v>
       </c>
       <c r="C63" t="n">
-        <v>0.2080598588002981</v>
+        <v>0.2047337139896602</v>
       </c>
     </row>
     <row r="64">
@@ -1132,10 +1132,10 @@
         <v>0.62</v>
       </c>
       <c r="B64" t="n">
-        <v>0.155404</v>
+        <v>0.153196</v>
       </c>
       <c r="C64" t="n">
-        <v>0.2085189449810256</v>
+        <v>0.2048958760346337</v>
       </c>
     </row>
     <row r="65">
@@ -1143,10 +1143,10 @@
         <v>0.63</v>
       </c>
       <c r="B65" t="n">
-        <v>0.155496</v>
+        <v>0.153104</v>
       </c>
       <c r="C65" t="n">
-        <v>0.2090038256013511</v>
+        <v>0.2050852250065811</v>
       </c>
     </row>
     <row r="66">
@@ -1154,10 +1154,10 @@
         <v>0.64</v>
       </c>
       <c r="B66" t="n">
-        <v>0.155588</v>
+        <v>0.153012</v>
       </c>
       <c r="C66" t="n">
-        <v>0.2095143215725359</v>
+        <v>0.2053016856823149</v>
       </c>
     </row>
     <row r="67">
@@ -1165,10 +1165,10 @@
         <v>0.65</v>
       </c>
       <c r="B67" t="n">
-        <v>0.15568</v>
+        <v>0.15292</v>
       </c>
       <c r="C67" t="n">
-        <v>0.2100502461317292</v>
+        <v>0.2055451724074297</v>
       </c>
     </row>
     <row r="68">
@@ -1176,10 +1176,10 @@
         <v>0.66</v>
       </c>
       <c r="B68" t="n">
-        <v>0.155772</v>
+        <v>0.152828</v>
       </c>
       <c r="C68" t="n">
-        <v>0.210611405161259</v>
+        <v>0.2058155892637873</v>
       </c>
     </row>
     <row r="69">
@@ -1187,10 +1187,10 @@
         <v>0.67</v>
       </c>
       <c r="B69" t="n">
-        <v>0.155864</v>
+        <v>0.152736</v>
       </c>
       <c r="C69" t="n">
-        <v>0.2111975975147445</v>
+        <v>0.2061128302556636</v>
       </c>
     </row>
     <row r="70">
@@ -1198,10 +1198,10 @@
         <v>0.68</v>
       </c>
       <c r="B70" t="n">
-        <v>0.155956</v>
+        <v>0.152644</v>
       </c>
       <c r="C70" t="n">
-        <v>0.2118086153488568</v>
+        <v>0.2064367795137291</v>
       </c>
     </row>
     <row r="71">
@@ -1209,10 +1209,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="B71" t="n">
-        <v>0.156048</v>
+        <v>0.152552</v>
       </c>
       <c r="C71" t="n">
-        <v>0.2124442444595758</v>
+        <v>0.2067873115159632</v>
       </c>
     </row>
     <row r="72">
@@ -1220,10 +1220,10 @@
         <v>0.7</v>
       </c>
       <c r="B72" t="n">
-        <v>0.15614</v>
+        <v>0.15246</v>
       </c>
       <c r="C72" t="n">
-        <v>0.2131042646218043</v>
+        <v>0.2071642913245427</v>
       </c>
     </row>
     <row r="73">
@@ -1231,10 +1231,10 @@
         <v>0.71</v>
       </c>
       <c r="B73" t="n">
-        <v>0.156232</v>
+        <v>0.152368</v>
       </c>
       <c r="C73" t="n">
-        <v>0.2137884499312346</v>
+        <v>0.2075675748376899</v>
       </c>
     </row>
     <row r="74">
@@ -1242,10 +1242,10 @@
         <v>0.72</v>
       </c>
       <c r="B74" t="n">
-        <v>0.156324</v>
+        <v>0.152276</v>
       </c>
       <c r="C74" t="n">
-        <v>0.2144965691473875</v>
+        <v>0.2079970090554189</v>
       </c>
     </row>
     <row r="75">
@@ -1253,10 +1253,10 @@
         <v>0.73</v>
       </c>
       <c r="B75" t="n">
-        <v>0.156416</v>
+        <v>0.152184</v>
       </c>
       <c r="C75" t="n">
-        <v>0.2152283860367865</v>
+        <v>0.2084524323580802</v>
       </c>
     </row>
     <row r="76">
@@ -1264,10 +1264,10 @@
         <v>0.74</v>
       </c>
       <c r="B76" t="n">
-        <v>0.156508</v>
+        <v>0.152092</v>
       </c>
       <c r="C76" t="n">
-        <v>0.2159836597152664</v>
+        <v>0.2089336747965727</v>
       </c>
     </row>
     <row r="77">
@@ -1275,10 +1275,10 @@
         <v>0.75</v>
       </c>
       <c r="B77" t="n">
-        <v>0.1566</v>
+        <v>0.152</v>
       </c>
       <c r="C77" t="n">
-        <v>0.2167621449884642</v>
+        <v>0.2094405583930677</v>
       </c>
     </row>
     <row r="78">
@@ -1286,10 +1286,10 @@
         <v>0.76</v>
       </c>
       <c r="B78" t="n">
-        <v>0.156692</v>
+        <v>0.151908</v>
       </c>
       <c r="C78" t="n">
-        <v>0.2175635926895858</v>
+        <v>0.2099728974510758</v>
       </c>
     </row>
     <row r="79">
@@ -1297,10 +1297,10 @@
         <v>0.77</v>
       </c>
       <c r="B79" t="n">
-        <v>0.156784</v>
+        <v>0.151816</v>
       </c>
       <c r="C79" t="n">
-        <v>0.2183877500135939</v>
+        <v>0.2105304988736786</v>
       </c>
     </row>
     <row r="80">
@@ -1308,10 +1308,10 @@
         <v>0.78</v>
       </c>
       <c r="B80" t="n">
-        <v>0.156876</v>
+        <v>0.151724</v>
       </c>
       <c r="C80" t="n">
-        <v>0.2192343608470169</v>
+        <v>0.2111131624887468</v>
       </c>
     </row>
     <row r="81">
@@ -1319,10 +1319,10 @@
         <v>0.79</v>
       </c>
       <c r="B81" t="n">
-        <v>0.156968</v>
+        <v>0.151632</v>
       </c>
       <c r="C81" t="n">
-        <v>0.2201031660926303</v>
+        <v>0.2117206813799729</v>
       </c>
     </row>
     <row r="82">
@@ -1330,10 +1330,10 @@
         <v>0.8</v>
       </c>
       <c r="B82" t="n">
-        <v>0.15706</v>
+        <v>0.15154</v>
       </c>
       <c r="C82" t="n">
-        <v>0.2209939039883227</v>
+        <v>0.2123528422225613</v>
       </c>
     </row>
     <row r="83">
@@ -1341,10 +1341,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="B83" t="n">
-        <v>0.157152</v>
+        <v>0.151448</v>
       </c>
       <c r="C83" t="n">
-        <v>0.2219063104195102</v>
+        <v>0.2130094256224358</v>
       </c>
     </row>
     <row r="84">
@@ -1352,10 +1352,10 @@
         <v>0.82</v>
       </c>
       <c r="B84" t="n">
-        <v>0.157244</v>
+        <v>0.151356</v>
       </c>
       <c r="C84" t="n">
-        <v>0.2228401192245238</v>
+        <v>0.2136902064578534</v>
       </c>
     </row>
     <row r="85">
@@ -1363,10 +1363,10 @@
         <v>0.83</v>
       </c>
       <c r="B85" t="n">
-        <v>0.157336</v>
+        <v>0.151264</v>
       </c>
       <c r="C85" t="n">
-        <v>0.2237950624924509</v>
+        <v>0.2143949542223417</v>
       </c>
     </row>
     <row r="86">
@@ -1374,10 +1374,10 @@
         <v>0.84</v>
       </c>
       <c r="B86" t="n">
-        <v>0.157428</v>
+        <v>0.151172</v>
       </c>
       <c r="C86" t="n">
-        <v>0.2247708708529644</v>
+        <v>0.2151234333679155</v>
       </c>
     </row>
     <row r="87">
@@ -1385,10 +1385,10 @@
         <v>0.85</v>
       </c>
       <c r="B87" t="n">
-        <v>0.15752</v>
+        <v>0.15108</v>
       </c>
       <c r="C87" t="n">
-        <v>0.2257672737577348</v>
+        <v>0.215875403647567</v>
       </c>
     </row>
     <row r="88">
@@ -1396,10 +1396,10 @@
         <v>0.86</v>
       </c>
       <c r="B88" t="n">
-        <v>0.157612</v>
+        <v>0.150988</v>
       </c>
       <c r="C88" t="n">
-        <v>0.226783999753069</v>
+        <v>0.2166506204560698</v>
       </c>
     </row>
     <row r="89">
@@ -1407,10 +1407,10 @@
         <v>0.87</v>
       </c>
       <c r="B89" t="n">
-        <v>0.157704</v>
+        <v>0.150896</v>
       </c>
       <c r="C89" t="n">
-        <v>0.2278207767434744</v>
+        <v>0.2174488351681839</v>
       </c>
     </row>
     <row r="90">
@@ -1418,10 +1418,10 @@
         <v>0.88</v>
       </c>
       <c r="B90" t="n">
-        <v>0.157796</v>
+        <v>0.150804</v>
       </c>
       <c r="C90" t="n">
-        <v>0.2288773322458998</v>
+        <v>0.2182697954734003</v>
       </c>
     </row>
     <row r="91">
@@ -1429,10 +1429,10 @@
         <v>0.89</v>
       </c>
       <c r="B91" t="n">
-        <v>0.157888</v>
+        <v>0.150712</v>
       </c>
       <c r="C91" t="n">
-        <v>0.2299533936344493</v>
+        <v>0.2191132457064155</v>
       </c>
     </row>
     <row r="92">
@@ -1440,10 +1440,10 @@
         <v>0.9</v>
       </c>
       <c r="B92" t="n">
-        <v>0.15798</v>
+        <v>0.15062</v>
       </c>
       <c r="C92" t="n">
-        <v>0.2310486883754158</v>
+        <v>0.2199789271725817</v>
       </c>
     </row>
     <row r="93">
@@ -1451,10 +1451,10 @@
         <v>0.91</v>
       </c>
       <c r="B93" t="n">
-        <v>0.158072</v>
+        <v>0.150528</v>
       </c>
       <c r="C93" t="n">
-        <v>0.2321629442525228</v>
+        <v>0.220866578467635</v>
       </c>
     </row>
     <row r="94">
@@ -1462,10 +1462,10 @@
         <v>0.92</v>
       </c>
       <c r="B94" t="n">
-        <v>0.158164</v>
+        <v>0.150436</v>
       </c>
       <c r="C94" t="n">
-        <v>0.233295889582307</v>
+        <v>0.2217759357910592</v>
       </c>
     </row>
     <row r="95">
@@ -1473,10 +1473,10 @@
         <v>0.93</v>
       </c>
       <c r="B95" t="n">
-        <v>0.158256</v>
+        <v>0.150344</v>
       </c>
       <c r="C95" t="n">
-        <v>0.2344472534196125</v>
+        <v>0.2227067332524996</v>
       </c>
     </row>
     <row r="96">
@@ -1484,10 +1484,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="B96" t="n">
-        <v>0.158348</v>
+        <v>0.150252</v>
       </c>
       <c r="C96" t="n">
-        <v>0.2356167657532036</v>
+        <v>0.2236587031707016</v>
       </c>
     </row>
     <row r="97">
@@ -1495,10 +1495,10 @@
         <v>0.95</v>
       </c>
       <c r="B97" t="n">
-        <v>0.15844</v>
+        <v>0.15016</v>
       </c>
       <c r="C97" t="n">
-        <v>0.2368041576915405</v>
+        <v>0.2246315763644996</v>
       </c>
     </row>
     <row r="98">
@@ -1506,10 +1506,10 @@
         <v>0.96</v>
       </c>
       <c r="B98" t="n">
-        <v>0.158532</v>
+        <v>0.150068</v>
       </c>
       <c r="C98" t="n">
-        <v>0.2380091616387907</v>
+        <v>0.225625082435442</v>
       </c>
     </row>
     <row r="99">
@@ -1517,10 +1517,10 @@
         <v>0.97</v>
       </c>
       <c r="B99" t="n">
-        <v>0.158624</v>
+        <v>0.149976</v>
       </c>
       <c r="C99" t="n">
-        <v>0.2392315114611785</v>
+        <v>0.2266389500416908</v>
       </c>
     </row>
     <row r="100">
@@ -1528,10 +1528,10 @@
         <v>0.98</v>
       </c>
       <c r="B100" t="n">
-        <v>0.158716</v>
+        <v>0.149884</v>
       </c>
       <c r="C100" t="n">
-        <v>0.2404709426438047</v>
+        <v>0.2276729071628858</v>
       </c>
     </row>
     <row r="101">
@@ -1539,10 +1539,10 @@
         <v>0.99</v>
       </c>
       <c r="B101" t="n">
-        <v>0.158808</v>
+        <v>0.149792</v>
       </c>
       <c r="C101" t="n">
-        <v>0.2417271924380871</v>
+        <v>0.2287266813557177</v>
       </c>
     </row>
     <row r="102">
@@ -1550,10 +1550,10 @@
         <v>1</v>
       </c>
       <c r="B102" t="n">
-        <v>0.1589</v>
+        <v>0.1497</v>
       </c>
       <c r="C102" t="n">
-        <v>0.243</v>
+        <v>0.2298</v>
       </c>
     </row>
   </sheetData>
